--- a/data/trans_camb/P62-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P62-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-35,45; -10,83</t>
+          <t>-35,4; -10,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 0,38</t>
+          <t>-22,2; 0,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 2,11</t>
+          <t>-20,82; 1,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-28,34; -0,39</t>
+          <t>-27,64; -0,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 5,62</t>
+          <t>-20,76; 6,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 15,88</t>
+          <t>-8,66; 15,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,55; -10,42</t>
+          <t>-29,67; -10,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,01; -0,94</t>
+          <t>-20,06; -1,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 4,18</t>
+          <t>-13,52; 4,24</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,37; -15,52</t>
+          <t>-43,92; -15,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 1,53</t>
+          <t>-27,25; 1,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 2,9</t>
+          <t>-25,49; 2,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,71; -1,07</t>
+          <t>-52,7; -2,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 13,48</t>
+          <t>-39,45; 18,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 42,34</t>
+          <t>-16,24; 42,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,4; -17,66</t>
+          <t>-43,65; -18,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,49; -1,86</t>
+          <t>-29,35; -2,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 7,21</t>
+          <t>-19,63; 7,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-32,54; -9,7</t>
+          <t>-32,41; -9,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-32,57; -9,71</t>
+          <t>-33,1; -8,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 2,61</t>
+          <t>-18,28; 2,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 13,35</t>
+          <t>-5,89; 14,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 11,66</t>
+          <t>-5,88; 12,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,16; 37,28</t>
+          <t>17,9; 37,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 4,03</t>
+          <t>-12,11; 4,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 1,88</t>
+          <t>-14,72; 2,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,4; 24,64</t>
+          <t>8,86; 25,42</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,01; -13,26</t>
+          <t>-38,04; -12,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,32; -12,7</t>
+          <t>-38,98; -12,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 3,32</t>
+          <t>-21,21; 3,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 102,64</t>
+          <t>-25,51; 102,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 84,59</t>
+          <t>-25,77; 93,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,1; 281,07</t>
+          <t>74,15; 303,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 10,45</t>
+          <t>-24,72; 10,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 4,84</t>
+          <t>-29,9; 7,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 64,11</t>
+          <t>17,83; 65,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,0; -11,64</t>
+          <t>-29,9; -11,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,2; -6,8</t>
+          <t>-24,52; -6,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 8,98</t>
+          <t>-10,59; 8,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,43; 33,06</t>
+          <t>9,39; 31,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,08; 42,49</t>
+          <t>16,43; 43,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,85; 45,72</t>
+          <t>24,33; 47,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 5,12</t>
+          <t>-10,05; 4,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 11,88</t>
+          <t>-4,25; 11,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,59; 22,59</t>
+          <t>7,39; 22,92</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,8; -17,44</t>
+          <t>-38,36; -17,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,82; -10,03</t>
+          <t>-31,38; -10,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 13,22</t>
+          <t>-13,6; 12,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39,57; 252,95</t>
+          <t>35,84; 230,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66,75; 322,16</t>
+          <t>60,44; 297,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>93,87; 350,03</t>
+          <t>88,74; 354,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 10,87</t>
+          <t>-17,92; 10,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 25,47</t>
+          <t>-7,48; 25,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,98; 47,96</t>
+          <t>12,76; 48,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,88; -14,29</t>
+          <t>-25,48; -13,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,19; -10,76</t>
+          <t>-21,68; -10,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,61; -0,02</t>
+          <t>-13,41; -0,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 3,81</t>
+          <t>-8,76; 3,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 10,66</t>
+          <t>-2,15; 10,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,55; 58,95</t>
+          <t>6,93; 58,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,87; -6,97</t>
+          <t>-15,77; -7,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,87; -2,09</t>
+          <t>-11,06; -1,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 28,04</t>
+          <t>-0,79; 28,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,57; -21,8</t>
+          <t>-35,77; -21,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,65; -16,07</t>
+          <t>-30,55; -16,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 0,05</t>
+          <t>-19,07; -0,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 16,11</t>
+          <t>-27,42; 14,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 44,36</t>
+          <t>-6,98; 42,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,19; 233,23</t>
+          <t>23,93; 249,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,88; -14,72</t>
+          <t>-29,88; -14,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,47; -4,23</t>
+          <t>-20,84; -4,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 58,27</t>
+          <t>-1,42; 58,89</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 1,62</t>
+          <t>-16,54; 1,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 4,57</t>
+          <t>-14,42; 4,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 18,67</t>
+          <t>-0,28; 19,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,55; 17,09</t>
+          <t>4,26; 17,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,1; 17,29</t>
+          <t>3,9; 17,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,28; 25,08</t>
+          <t>12,45; 26,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 10,26</t>
+          <t>0,12; 10,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,58</t>
+          <t>1,15; 11,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,09; 21,77</t>
+          <t>10,72; 21,55</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,4; 3,71</t>
+          <t>-29,36; 4,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 10,53</t>
+          <t>-25,08; 10,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 41,64</t>
+          <t>-0,52; 44,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,59; 68,1</t>
+          <t>13,11; 72,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,94; 69,43</t>
+          <t>12,03; 68,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,28; 100,6</t>
+          <t>37,65; 107,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 31,32</t>
+          <t>0,24; 31,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,86; 35,46</t>
+          <t>3,02; 34,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28,13; 68,04</t>
+          <t>27,74; 67,65</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 6,91</t>
+          <t>-0,88; 7,19</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 2,32</t>
+          <t>-3,43; 2,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 5,11</t>
+          <t>-2,0; 5,18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 6,05</t>
+          <t>-1,0; 6,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 5,3</t>
+          <t>-2,13; 5,48</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,62</t>
+          <t>0,57; 8,02</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,49</t>
+          <t>-0,34; 5,68</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,9</t>
+          <t>-2,27; 3,95</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,58</t>
+          <t>-0,41; 5,55</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 323,66</t>
+          <t>-21,59; 387,23</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-69,91; 115,31</t>
+          <t>-68,1; 141,45</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,71; 218,11</t>
+          <t>-43,09; 251,55</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 29,14</t>
+          <t>-4,07; 31,28</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 25,63</t>
+          <t>-8,68; 26,86</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,65; 37,03</t>
+          <t>2,34; 40,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 31,81</t>
+          <t>-1,67; 33,19</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 23,4</t>
+          <t>-11,77; 22,52</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 32,94</t>
+          <t>-2,13; 32,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -6,91</t>
+          <t>-14,08; -6,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -4,74</t>
+          <t>-11,84; -4,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 5,33</t>
+          <t>-3,33; 4,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,13</t>
+          <t>1,99; 6,93</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,24</t>
+          <t>2,73; 8,06</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,15; 35,24</t>
+          <t>12,16; 34,87</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,22</t>
+          <t>-2,23; 2,01</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,83</t>
+          <t>-0,47; 3,84</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,15; 22,08</t>
+          <t>8,76; 24,07</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-24,2; -13,09</t>
+          <t>-25,16; -12,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,3; -9,08</t>
+          <t>-20,81; -8,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 10,35</t>
+          <t>-5,85; 9,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,09; 30,92</t>
+          <t>7,62; 29,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,32; 35,1</t>
+          <t>10,52; 34,61</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>48,19; 145,6</t>
+          <t>47,89; 143,36</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 6,54</t>
+          <t>-6,01; 5,86</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 11,22</t>
+          <t>-1,29; 11,18</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25,35; 61,18</t>
+          <t>24,32; 67,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P62-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P62-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-9,06</t>
+          <t>-6,96</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,17</t>
+          <t>-3,5</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-35,4; -10,73</t>
+          <t>-35,29; -11,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 0,92</t>
+          <t>-21,65; 0,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 1,48</t>
+          <t>-16,76; 3,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,64; -0,22</t>
+          <t>-28,96; -2,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 6,62</t>
+          <t>-21,97; 5,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 15,73</t>
+          <t>-10,34; 13,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,67; -10,47</t>
+          <t>-29,75; -10,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,06; -1,7</t>
+          <t>-19,81; -1,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 4,24</t>
+          <t>-11,36; 5,28</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-11,83%</t>
+          <t>-9,08%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-6,58%</t>
+          <t>-5,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,92; -15,23</t>
+          <t>-43,84; -16,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 1,22</t>
+          <t>-27,01; -0,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,49; 2,25</t>
+          <t>-20,31; 4,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,7; -2,15</t>
+          <t>-53,86; -5,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 18,18</t>
+          <t>-40,75; 14,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 42,05</t>
+          <t>-18,25; 35,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,65; -18,16</t>
+          <t>-44,5; -18,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,35; -2,62</t>
+          <t>-29,09; -2,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 7,24</t>
+          <t>-16,63; 9,02</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-7,98</t>
+          <t>-8,57</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,57</t>
+          <t>28,58</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16,76</t>
+          <t>16,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-32,41; -9,77</t>
+          <t>-32,88; -8,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-33,1; -8,77</t>
+          <t>-32,92; -8,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 2,51</t>
+          <t>-18,67; 1,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 14,15</t>
+          <t>-6,3; 13,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 12,49</t>
+          <t>-7,68; 12,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,9; 37,69</t>
+          <t>19,13; 38,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 4,28</t>
+          <t>-12,05; 5,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 2,82</t>
+          <t>-14,69; 2,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 25,42</t>
+          <t>8,05; 24,79</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-9,87%</t>
+          <t>-10,6%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>152,56%</t>
+          <t>152,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,04; -12,97</t>
+          <t>-38,88; -11,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,98; -12,07</t>
+          <t>-38,92; -11,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 3,13</t>
+          <t>-21,5; 2,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 102,42</t>
+          <t>-27,74; 104,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 93,97</t>
+          <t>-30,46; 90,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,15; 303,38</t>
+          <t>72,16; 291,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 10,93</t>
+          <t>-25,17; 13,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 7,74</t>
+          <t>-30,45; 4,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,83; 65,62</t>
+          <t>16,17; 63,96</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-1,79</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,66</t>
+          <t>34,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,34</t>
+          <t>14,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,9; -11,57</t>
+          <t>-30,06; -11,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,52; -6,87</t>
+          <t>-24,69; -6,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 8,64</t>
+          <t>-10,98; 7,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 31,81</t>
+          <t>9,84; 32,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 43,11</t>
+          <t>17,32; 44,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,33; 47,08</t>
+          <t>23,65; 44,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 4,95</t>
+          <t>-10,07; 4,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 11,85</t>
+          <t>-3,39; 11,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 22,92</t>
+          <t>6,76; 22,07</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-0,49%</t>
+          <t>-2,43%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>183,35%</t>
+          <t>178,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,36; -17,15</t>
+          <t>-38,02; -16,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,38; -10,21</t>
+          <t>-31,38; -9,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 12,75</t>
+          <t>-14,04; 10,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,84; 230,63</t>
+          <t>38,59; 249,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,44; 297,15</t>
+          <t>65,44; 325,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88,74; 354,7</t>
+          <t>93,39; 344,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 10,42</t>
+          <t>-18,15; 10,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 25,54</t>
+          <t>-6,1; 25,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,76; 48,22</t>
+          <t>11,97; 47,74</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-6,5</t>
+          <t>-5,71</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,48</t>
+          <t>8,55</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,24</t>
+          <t>0,66</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,48; -13,72</t>
+          <t>-26,12; -14,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-21,68; -10,88</t>
+          <t>-21,76; -10,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,41; -0,08</t>
+          <t>-11,76; 0,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 3,66</t>
+          <t>-8,07; 3,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 10,6</t>
+          <t>-1,95; 10,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 58,09</t>
+          <t>3,0; 14,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -7,13</t>
+          <t>-15,98; -7,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,06; -1,91</t>
+          <t>-11,32; -1,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 28,8</t>
+          <t>-3,67; 5,56</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-9,45%</t>
+          <t>-8,3%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>116,49%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,77; -21,45</t>
+          <t>-36,14; -21,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,55; -16,44</t>
+          <t>-30,8; -15,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,07; -0,13</t>
+          <t>-16,66; 0,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 14,46</t>
+          <t>-26,43; 15,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 42,93</t>
+          <t>-6,24; 41,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,93; 249,96</t>
+          <t>9,47; 58,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,88; -14,7</t>
+          <t>-29,78; -14,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,84; -4,09</t>
+          <t>-21,13; -4,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 58,89</t>
+          <t>-6,87; 11,48</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>7,84</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,19</t>
+          <t>18,52</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16,35</t>
+          <t>15,39</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 1,92</t>
+          <t>-15,98; 1,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 4,46</t>
+          <t>-14,05; 4,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 19,77</t>
+          <t>-2,64; 17,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,26; 17,61</t>
+          <t>4,2; 16,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,9; 17,17</t>
+          <t>4,07; 16,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,45; 26,01</t>
+          <t>12,48; 24,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 10,21</t>
+          <t>0,35; 11,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,43</t>
+          <t>1,65; 11,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,72; 21,55</t>
+          <t>9,87; 20,21</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 4,14</t>
+          <t>-28,34; 4,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 10,12</t>
+          <t>-24,97; 9,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 44,53</t>
+          <t>-4,49; 38,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,11; 72,48</t>
+          <t>12,35; 68,47</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,03; 68,06</t>
+          <t>12,83; 65,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,65; 107,83</t>
+          <t>38,21; 106,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,24; 31,54</t>
+          <t>0,91; 33,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,02; 34,61</t>
+          <t>4,33; 36,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>27,74; 67,65</t>
+          <t>25,62; 62,32</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,28</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 7,19</t>
+          <t>-1,16; 6,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,9</t>
+          <t>-3,35; 2,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 5,18</t>
+          <t>-2,19; 4,73</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 6,25</t>
+          <t>-1,03; 5,94</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 5,48</t>
+          <t>-2,13; 5,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,57; 8,02</t>
+          <t>-0,13; 6,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,68</t>
+          <t>-0,57; 5,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 3,95</t>
+          <t>-1,84; 3,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 5,55</t>
+          <t>-0,54; 5,3</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 387,23</t>
+          <t>-38,47; 315,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-68,1; 141,45</t>
+          <t>-71,63; 127,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-43,09; 251,55</t>
+          <t>-52,28; 203,93</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 31,28</t>
+          <t>-4,2; 29,37</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 26,86</t>
+          <t>-9,04; 27,06</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,34; 40,06</t>
+          <t>-0,61; 31,85</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 33,19</t>
+          <t>-3,69; 33,33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 22,52</t>
+          <t>-9,85; 23,08</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 32,69</t>
+          <t>-2,64; 31,71</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,04</t>
+          <t>12,47</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>12,77</t>
+          <t>9,48</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-14,08; -6,67</t>
+          <t>-14,12; -7,23</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -4,7</t>
+          <t>-11,48; -4,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 4,81</t>
+          <t>-2,15; 5,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,93</t>
+          <t>1,87; 7,03</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,06</t>
+          <t>2,81; 8,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,16; 34,87</t>
+          <t>10,07; 15,01</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,01</t>
+          <t>-2,18; 1,99</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,84</t>
+          <t>-0,43; 3,95</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8,76; 24,07</t>
+          <t>7,2; 11,7</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-25,16; -12,91</t>
+          <t>-25,0; -13,75</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -8,84</t>
+          <t>-20,18; -8,8</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 9,06</t>
+          <t>-3,86; 10,23</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,62; 29,76</t>
+          <t>7,23; 30,23</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,52; 34,61</t>
+          <t>10,67; 34,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>47,89; 143,36</t>
+          <t>38,75; 64,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 5,86</t>
+          <t>-6,01; 5,78</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 11,18</t>
+          <t>-1,14; 11,46</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>24,32; 67,43</t>
+          <t>19,42; 33,87</t>
         </is>
       </c>
     </row>
